--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/4. 人口数变更.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/4. 人口数变更.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="210">
   <si>
     <t>业务属性</t>
   </si>
@@ -314,9 +314,6 @@
   </si>
   <si>
     <t>自由文本，非空</t>
-  </si>
-  <si>
-    <t>NVARCHAR2</t>
   </si>
   <si>
     <t>支持中文、自由文本</t>
@@ -659,7 +656,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -721,13 +718,6 @@
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1288,48 +1278,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1339,97 +1332,94 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2365,13 +2355,13 @@
         <v>77</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>79</v>
       </c>
       <c r="R6" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>75</v>
@@ -2395,7 +2385,7 @@
         <v>83</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>85</v>
@@ -2404,21 +2394,21 @@
         <v>86</v>
       </c>
       <c r="AC6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD6" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD6" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:30">
       <c r="A7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>69</v>
@@ -2433,10 +2423,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>75</v>
@@ -2457,13 +2447,13 @@
         <v>77</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R7" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>75</v>
@@ -2487,7 +2477,7 @@
         <v>83</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>85</v>
@@ -2496,21 +2486,21 @@
         <v>86</v>
       </c>
       <c r="AC7" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD7" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD7" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:30">
       <c r="A8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>69</v>
@@ -2525,10 +2515,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2579,10 +2569,10 @@
         <v>83</v>
       </c>
       <c r="Z8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="AB8" s="4" t="s">
         <v>86</v>
@@ -2596,13 +2586,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:30">
       <c r="A9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -2617,10 +2607,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>75</v>
@@ -2671,10 +2661,10 @@
         <v>83</v>
       </c>
       <c r="Z9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA9" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="AB9" s="6" t="s">
         <v>86</v>
@@ -2688,13 +2678,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:30">
       <c r="A10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>69</v>
@@ -2709,10 +2699,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -2733,10 +2723,10 @@
         <v>77</v>
       </c>
       <c r="P10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q10" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R10" s="4">
         <v>22</v>
@@ -2745,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U10" s="4" t="s">
         <v>80</v>
@@ -2763,10 +2753,10 @@
         <v>83</v>
       </c>
       <c r="Z10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>86</v>
@@ -2780,13 +2770,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:30">
       <c r="A11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -2801,10 +2791,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>75</v>
@@ -2825,10 +2815,10 @@
         <v>77</v>
       </c>
       <c r="P11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q11" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R11" s="6">
         <v>22</v>
@@ -2837,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>80</v>
@@ -2855,10 +2845,10 @@
         <v>83</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AB11" s="6" t="s">
         <v>86</v>
@@ -2872,13 +2862,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:30">
       <c r="A12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>69</v>
@@ -2893,10 +2883,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -2917,10 +2907,10 @@
         <v>77</v>
       </c>
       <c r="P12" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q12" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="R12" s="4">
         <v>7</v>
@@ -2947,10 +2937,10 @@
         <v>83</v>
       </c>
       <c r="Z12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA12" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="AA12" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="AB12" s="4" t="s">
         <v>86</v>
@@ -2964,13 +2954,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:30">
       <c r="A13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>69</v>
@@ -2985,10 +2975,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>75</v>
@@ -3009,10 +2999,10 @@
         <v>77</v>
       </c>
       <c r="P13" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="R13" s="6">
         <v>7</v>
@@ -3039,10 +3029,10 @@
         <v>83</v>
       </c>
       <c r="Z13" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA13" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="AA13" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="AB13" s="6" t="s">
         <v>86</v>
@@ -3056,13 +3046,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:30">
       <c r="A14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
@@ -3077,10 +3067,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>75</v>
@@ -3101,10 +3091,10 @@
         <v>77</v>
       </c>
       <c r="P14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q14" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R14" s="4">
         <v>22</v>
@@ -3131,10 +3121,10 @@
         <v>83</v>
       </c>
       <c r="Z14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA14" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="AA14" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="AB14" s="4" t="s">
         <v>86</v>
@@ -3148,13 +3138,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:30">
       <c r="A15" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>69</v>
@@ -3169,10 +3159,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>75</v>
@@ -3193,10 +3183,10 @@
         <v>77</v>
       </c>
       <c r="P15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q15" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="R15" s="6">
         <v>7</v>
@@ -3223,10 +3213,10 @@
         <v>83</v>
       </c>
       <c r="Z15" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA15" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="AA15" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="AB15" s="6" t="s">
         <v>86</v>
@@ -3240,13 +3230,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:30">
       <c r="A16" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
@@ -3261,10 +3251,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>75</v>
@@ -3285,10 +3275,10 @@
         <v>77</v>
       </c>
       <c r="P16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q16" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R16" s="4">
         <v>22</v>
@@ -3315,10 +3305,10 @@
         <v>83</v>
       </c>
       <c r="Z16" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA16" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="AA16" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="AB16" s="4" t="s">
         <v>86</v>
@@ -3332,13 +3322,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:30">
       <c r="A17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>69</v>
@@ -3353,10 +3343,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>75</v>
@@ -3377,10 +3367,10 @@
         <v>77</v>
       </c>
       <c r="P17" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="R17" s="6">
         <v>7</v>
@@ -3407,13 +3397,13 @@
         <v>83</v>
       </c>
       <c r="Z17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="AA17" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="AB17" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC17" s="25" t="s">
         <v>87</v>
@@ -3424,13 +3414,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:30">
       <c r="A18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>69</v>
@@ -3445,7 +3435,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>99</v>
@@ -3469,13 +3459,13 @@
         <v>77</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="4" t="s">
         <v>79</v>
       </c>
       <c r="R18" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>75</v>
@@ -3499,7 +3489,7 @@
         <v>83</v>
       </c>
       <c r="Z18" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA18" s="5" t="s">
         <v>85</v>
@@ -3508,21 +3498,21 @@
         <v>86</v>
       </c>
       <c r="AC18" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD18" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD18" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:30">
       <c r="A19" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>69</v>
@@ -3537,10 +3527,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>75</v>
@@ -3561,10 +3551,10 @@
         <v>77</v>
       </c>
       <c r="P19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q19" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="R19" s="6">
         <v>7</v>
@@ -3591,10 +3581,10 @@
         <v>83</v>
       </c>
       <c r="Z19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA19" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="AB19" s="6" t="s">
         <v>86</v>
@@ -3608,13 +3598,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:30">
       <c r="A20" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>69</v>
@@ -3629,10 +3619,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>75</v>
@@ -3683,30 +3673,30 @@
         <v>83</v>
       </c>
       <c r="Z20" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AA20" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC20" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD20" s="30" t="s">
         <v>189</v>
-      </c>
-      <c r="AD20" s="30" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:30">
       <c r="A21" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>69</v>
@@ -3721,10 +3711,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>75</v>
@@ -3775,30 +3765,30 @@
         <v>83</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB21" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC21" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD21" s="30" t="s">
         <v>189</v>
-      </c>
-      <c r="AD21" s="30" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:30">
       <c r="A22" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>69</v>
@@ -3813,10 +3803,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>75</v>
@@ -3870,10 +3860,10 @@
         <v>85</v>
       </c>
       <c r="AA22" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC22" s="23" t="s">
         <v>87</v>
@@ -3884,13 +3874,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:30">
       <c r="A23" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>69</v>
@@ -3905,10 +3895,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>75</v>
@@ -3929,7 +3919,7 @@
         <v>77</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>79</v>
@@ -3959,13 +3949,13 @@
         <v>83</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB23" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC23" s="25" t="s">
         <v>87</v>
@@ -3976,13 +3966,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:30">
       <c r="A24" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>69</v>
@@ -3997,10 +3987,10 @@
         <v>72</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>75</v>
@@ -4051,19 +4041,19 @@
         <v>83</v>
       </c>
       <c r="Z24" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AA24" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC24" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD24" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD24" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
